--- a/data/trans_camb/P12_3_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P12_3_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,76</t>
+          <t>2,01; 7,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,19</t>
+          <t>1,28; 7,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,49; 12,41</t>
+          <t>5,57; 12,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 10,03</t>
+          <t>4,48; 10,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,28</t>
+          <t>6,86; 13,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,4; 16,38</t>
+          <t>10,59; 16,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,23</t>
+          <t>4,11; 8,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 9,76</t>
+          <t>5,21; 9,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 13,78</t>
+          <t>9,17; 13,65</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,79; 95,25</t>
+          <t>18,68; 101,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,15; 89,67</t>
+          <t>11,42; 92,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,06; 158,5</t>
+          <t>55,85; 161,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,53; 95,71</t>
+          <t>35,4; 97,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,28; 127,44</t>
+          <t>53,73; 124,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,35; 158,14</t>
+          <t>82,93; 162,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,18; 86,45</t>
+          <t>35,47; 86,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,29; 101,1</t>
+          <t>46,01; 101,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>82,62; 141,85</t>
+          <t>81,62; 143,43</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,22</t>
+          <t>1,47; 4,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,82</t>
+          <t>1,08; 3,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,65</t>
+          <t>2,13; 6,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,35</t>
+          <t>2,15; 6,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,22</t>
+          <t>0,49; 4,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,28</t>
+          <t>1,34; 6,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,82</t>
+          <t>2,27; 4,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,5</t>
+          <t>1,34; 3,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,03</t>
+          <t>2,55; 6,06</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,59; 156,37</t>
+          <t>37,59; 160,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,24; 144,64</t>
+          <t>26,51; 137,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,75; 230,99</t>
+          <t>59,84; 235,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,3; 115,35</t>
+          <t>28,85; 113,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 74,78</t>
+          <t>7,18; 78,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,87; 108,5</t>
+          <t>21,07; 109,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,94; 110,66</t>
+          <t>41,82; 108,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,8; 80,77</t>
+          <t>24,86; 84,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,32; 136,57</t>
+          <t>50,99; 139,47</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,3</t>
+          <t>-1,27; 3,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,12</t>
+          <t>0,21; 5,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,4; 10,45</t>
+          <t>3,18; 10,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,2</t>
+          <t>-4,05; 2,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 0,66</t>
+          <t>-5,33; 0,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,99</t>
+          <t>-2,07; 3,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,55</t>
+          <t>-1,78; 2,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,17</t>
+          <t>-1,63; 2,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,2</t>
+          <t>1,66; 6,52</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 184,97</t>
+          <t>-38,69; 219,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,89; 323,78</t>
+          <t>0,52; 345,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68,22; 541,3</t>
+          <t>74,46; 570,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,9; 64,09</t>
+          <t>-49,34; 53,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,29; 15,24</t>
+          <t>-63,95; 12,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,06; 87,15</t>
+          <t>-24,75; 78,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-31,21; 71,31</t>
+          <t>-34,05; 68,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 57,62</t>
+          <t>-29,02; 62,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,62; 173,83</t>
+          <t>26,07; 172,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,16</t>
+          <t>1,68; 4,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,52</t>
+          <t>1,19; 3,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,56</t>
+          <t>2,38; 6,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,25; 6,36</t>
+          <t>3,32; 6,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,61</t>
+          <t>1,66; 4,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,14</t>
+          <t>2,19; 6,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,84</t>
+          <t>2,9; 4,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,79</t>
+          <t>1,74; 3,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,94</t>
+          <t>3,01; 5,96</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>31,64; 93,28</t>
+          <t>29,65; 92,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,04; 79,0</t>
+          <t>20,66; 81,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50,02; 142,69</t>
+          <t>47,63; 136,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,0; 81,86</t>
+          <t>36,87; 81,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,57; 59,19</t>
+          <t>18,16; 60,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,0; 77,99</t>
+          <t>25,73; 79,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,81; 77,62</t>
+          <t>39,47; 76,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>26,01; 59,86</t>
+          <t>23,7; 58,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>44,64; 92,42</t>
+          <t>43,33; 93,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_3_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P12_3_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,74</t>
+          <t>8,54</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,4</t>
+          <t>14,37</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,59</t>
+          <t>12,02</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,93</t>
+          <t>1,87; 7,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,26</t>
+          <t>1,48; 6,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 12,58</t>
+          <t>4,78; 11,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 10,13</t>
+          <t>4,84; 9,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 13,21</t>
+          <t>6,53; 13,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 16,33</t>
+          <t>11,25; 17,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,4</t>
+          <t>4,34; 8,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 9,72</t>
+          <t>5,33; 10,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 13,65</t>
+          <t>9,68; 14,11</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>116,1%</t>
+          <t>124,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>110,81%</t>
+          <t>114,98%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,68; 101,51</t>
+          <t>18,63; 96,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,42; 92,44</t>
+          <t>14,14; 86,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,85; 161,13</t>
+          <t>45,28; 145,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35,4; 97,33</t>
+          <t>36,98; 96,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,73; 124,43</t>
+          <t>51,82; 124,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,93; 162,92</t>
+          <t>88,38; 168,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,47; 86,07</t>
+          <t>38,57; 88,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>46,01; 101,74</t>
+          <t>46,62; 103,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,62; 143,43</t>
+          <t>86,12; 147,76</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,87</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,57</t>
+          <t>6,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,32</t>
+          <t>1,36; 4,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,83</t>
+          <t>0,86; 3,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,59</t>
+          <t>4,63; 7,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,24</t>
+          <t>2,36; 6,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,26</t>
+          <t>0,76; 4,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,3</t>
+          <t>4,16; 7,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,77</t>
+          <t>2,23; 4,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,62</t>
+          <t>1,19; 3,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,06</t>
+          <t>4,9; 7,35</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>143,27%</t>
+          <t>180,76%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>124,91%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,59; 160,17</t>
+          <t>31,34; 161,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,51; 137,15</t>
+          <t>21,55; 142,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,84; 235,79</t>
+          <t>110,99; 284,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,85; 113,61</t>
+          <t>31,78; 112,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 78,64</t>
+          <t>10,14; 78,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,07; 109,5</t>
+          <t>54,7; 140,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,82; 108,67</t>
+          <t>39,71; 107,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,86; 84,2</t>
+          <t>21,71; 79,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,99; 139,47</t>
+          <t>88,95; 168,58</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,34</t>
+          <t>5,3</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,83</t>
+          <t>3,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,53</t>
+          <t>-1,26; 3,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,37</t>
+          <t>0,41; 5,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 10,27</t>
+          <t>2,89; 8,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 2,9</t>
+          <t>-3,94; 3,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 0,59</t>
+          <t>-5,02; 0,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 3,91</t>
+          <t>-1,15; 4,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,48</t>
+          <t>-1,6; 2,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,2</t>
+          <t>-1,68; 2,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,52</t>
+          <t>1,49; 5,45</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>236,59%</t>
+          <t>197,93%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>80,49%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,69; 219,14</t>
+          <t>-36,86; 200,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 345,52</t>
+          <t>3,59; 330,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74,46; 570,02</t>
+          <t>65,6; 481,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,34; 53,54</t>
+          <t>-49,17; 60,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,95; 12,27</t>
+          <t>-60,97; 11,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 78,62</t>
+          <t>-14,29; 90,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,05; 68,65</t>
+          <t>-30,7; 70,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 62,38</t>
+          <t>-31,87; 62,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26,07; 172,12</t>
+          <t>24,1; 153,15</t>
         </is>
       </c>
     </row>
@@ -1282,14 +1282,14 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>5,49</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,77</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,77</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,22</t>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,61</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,71</t>
+          <t>5,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,18</t>
+          <t>1,72; 4,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,55</t>
+          <t>1,17; 3,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,33</t>
+          <t>4,17; 6,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,4</t>
+          <t>3,18; 6,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,69</t>
+          <t>1,56; 4,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,24</t>
+          <t>4,63; 7,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 4,86</t>
+          <t>2,92; 4,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,75</t>
+          <t>1,89; 3,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,96</t>
+          <t>4,91; 6,85</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>108,34%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>29,65; 92,28</t>
+          <t>31,62; 94,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,66; 81,7</t>
+          <t>20,4; 77,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,63; 136,39</t>
+          <t>72,93; 151,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36,87; 81,31</t>
+          <t>33,82; 81,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,16; 60,54</t>
+          <t>16,65; 58,68</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,73; 79,79</t>
+          <t>49,92; 98,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,47; 76,53</t>
+          <t>39,82; 76,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>23,7; 58,83</t>
+          <t>26,27; 58,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43,33; 93,58</t>
+          <t>67,98; 109,05</t>
         </is>
       </c>
     </row>
